--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -4,15 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="20115" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="21570" windowHeight="11175"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="TestCase" r:id="rId7" sheetId="4"/>
+    <sheet name="Multiple" sheetId="1" r:id="rId1"/>
+    <sheet name="TestCase" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:T35"/>
 </workbook>
 </file>
 
@@ -50,7 +49,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -397,20 +395,20 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="12.7109375"/>
-    <col min="2" max="2" customWidth="true" width="18.42578125"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -418,7 +416,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -426,7 +424,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -447,31 +445,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -43,6 +43,24 @@
   </si>
   <si>
     <t>Hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC ID </t>
+  </si>
+  <si>
+    <t>Rama</t>
+  </si>
+  <si>
+    <t>Shyam</t>
+  </si>
+  <si>
+    <t>Rama@gmail.com</t>
+  </si>
+  <si>
+    <t>Shyam@gmail.com</t>
+  </si>
+  <si>
+    <t>TC Status</t>
   </si>
 </sst>
 </file>
@@ -87,9 +105,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -392,43 +412,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="C4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -436,6 +493,8 @@
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
     <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="21570" windowHeight="11175"/>
+    <workbookView windowWidth="29400" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Multiple" sheetId="1" r:id="rId1"/>
     <sheet name="TestCase" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:T35"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -24,55 +36,86 @@
     <t>Email ID</t>
   </si>
   <si>
+    <t xml:space="preserve">TC ID </t>
+  </si>
+  <si>
+    <t>TC Status</t>
+  </si>
+  <si>
     <t>Jhon</t>
   </si>
   <si>
+    <t>Jhon@gmail.com</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>smith</t>
+  </si>
+  <si>
+    <t>smith@gmail.com</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
     <t>admin</t>
   </si>
   <si>
-    <t>Jhon@gmail.com</t>
-  </si>
-  <si>
-    <t>smith@gmail.com</t>
-  </si>
-  <si>
     <t>admin@gmail.com</t>
   </si>
   <si>
-    <t>smith</t>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Rama</t>
+  </si>
+  <si>
+    <t>Rama@gmail.com</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Shyam</t>
+  </si>
+  <si>
+    <t>Shyam@gmail.com</t>
+  </si>
+  <si>
+    <t>105</t>
   </si>
   <si>
     <t>Hello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC ID </t>
-  </si>
-  <si>
-    <t>Rama</t>
-  </si>
-  <si>
-    <t>Shyam</t>
-  </si>
-  <si>
-    <t>Rama@gmail.com</t>
-  </si>
-  <si>
-    <t>Shyam@gmail.com</t>
-  </si>
-  <si>
-    <t>TC Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -80,19 +123,347 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -100,22 +471,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -406,111 +1084,134 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.4296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>105</v>
-      </c>
+      <c r="E6" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B2" r:id="rId1" display="Jhon@gmail.com"/>
+    <hyperlink ref="B3" r:id="rId2" display="smith@gmail.com"/>
+    <hyperlink ref="B4" r:id="rId3" display="admin@gmail.com"/>
+    <hyperlink ref="B5" r:id="rId4" display="Rama@gmail.com"/>
+    <hyperlink ref="B6" r:id="rId5" display="Shyam@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -29,81 +29,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
-    <t>Email ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC ID </t>
-  </si>
-  <si>
-    <t>TC Status</t>
-  </si>
-  <si>
-    <t>Jhon</t>
-  </si>
-  <si>
-    <t>Jhon@gmail.com</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>smith</t>
   </si>
   <si>
     <t>smith@gmail.com</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>admin</t>
   </si>
   <si>
     <t>admin@gmail.com</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>Rama</t>
   </si>
   <si>
     <t>Rama@gmail.com</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>Shyam</t>
   </si>
   <si>
     <t>Shyam@gmail.com</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
     <t>Hello</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Ravi123</t>
+  </si>
+  <si>
+    <t>Ravi M B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -148,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +141,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +451,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -473,99 +459,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C6" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B3" r:id="rId1"/>
+    <hyperlink ref="B4" r:id="rId2"/>
+    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="B6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -576,7 +526,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="2445" windowWidth="21510" windowHeight="11175"/>
   </bookViews>
   <sheets>
-    <sheet name="EMPDATA" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="TestCase" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -64,10 +64,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>Ravi123</t>
-  </si>
-  <si>
-    <t>Ravi M B</t>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
   </si>
 </sst>
 </file>
@@ -464,10 +464,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="3"/>
     </row>

--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="21510" windowHeight="11175"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="15210" windowHeight="6495"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="TestCase" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <oleSize ref="A1:N20"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,9 +46,6 @@
     <t>admin@gmail.com</t>
   </si>
   <si>
-    <t>Rama</t>
-  </si>
-  <si>
     <t>Rama@gmail.com</t>
   </si>
   <si>
@@ -68,6 +65,9 @@
   </si>
   <si>
     <t>admin123</t>
+  </si>
+  <si>
+    <t>0235</t>
   </si>
 </sst>
 </file>
@@ -459,15 +459,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -491,19 +491,19 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -526,7 +526,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/TestData.xlsx
+++ b/data/TestData.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="15210" windowHeight="6495"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="21255" windowHeight="11175"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="TestCase" sheetId="2" r:id="rId2"/>
+    <sheet name="PIM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:N20"/>
+  <oleSize ref="A1:T35"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -55,9 +55,6 @@
     <t>Shyam@gmail.com</t>
   </si>
   <si>
-    <t>Hello</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
@@ -67,19 +64,50 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>0235</t>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>EmployeeID</t>
+  </si>
+  <si>
+    <t>Jhonson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de </t>
+  </si>
+  <si>
+    <t>hillary</t>
+  </si>
+  <si>
+    <t>023145</t>
+  </si>
+  <si>
+    <t>Edmund</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -104,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -127,11 +155,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -141,6 +180,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,31 +492,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -480,7 +525,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -489,16 +534,16 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -521,14 +566,52 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-    </row>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4"/>
+    <row r="4" spans="1:4"/>
+    <row r="5" spans="1:4"/>
+    <row r="6" spans="1:4"/>
+    <row r="7" spans="1:4"/>
+    <row r="8" spans="1:4"/>
+    <row r="9" spans="1:4"/>
+    <row r="10" spans="1:4"/>
+    <row r="11" spans="1:4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
